--- a/DosingApp/DosingApp/Resources/Invoices/Требование-накладная М-11 (шаблон).xlsx
+++ b/DosingApp/DosingApp/Resources/Invoices/Требование-накладная М-11 (шаблон).xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>от 30.10.97 № 71а</t>
   </si>
@@ -139,13 +139,7 @@
     <t>Весовщик</t>
   </si>
   <si>
-    <t xml:space="preserve">ООО "ЧЕРКИЗОВО-РАСТЕНИЕВОДСТВО" </t>
-  </si>
-  <si>
     <t>Ведущий Технолог</t>
-  </si>
-  <si>
-    <t>ОП Елецкое</t>
   </si>
   <si>
     <t xml:space="preserve">код аналитического учета </t>
@@ -707,6 +701,90 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -732,9 +810,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -760,87 +835,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1152,7 +1146,7 @@
       <c r="I1" s="37"/>
       <c r="J1" s="37"/>
       <c r="K1" s="38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1167,7 +1161,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1205,15 +1199,15 @@
       <c r="D5" s="4"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
+        <v>40</v>
+      </c>
+      <c r="G5" s="67"/>
+      <c r="H5" s="68"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="41"/>
+      <c r="K5" s="69"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
@@ -1227,31 +1221,27 @@
       <c r="I6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="70">
         <v>315006</v>
       </c>
-      <c r="K6" s="43"/>
+      <c r="K6" s="71"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
       <c r="I7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="55">
-        <v>36279727</v>
-      </c>
-      <c r="K7" s="56"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="83"/>
     </row>
     <row r="8" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
@@ -1267,38 +1257,38 @@
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="48" t="s">
+      <c r="B9" s="73"/>
+      <c r="C9" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="50" t="s">
+      <c r="E9" s="78"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="52"/>
-      <c r="I9" s="48" t="s">
+      <c r="H9" s="79"/>
+      <c r="I9" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48" t="s">
+      <c r="J9" s="56"/>
+      <c r="K9" s="56" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="76"/>
       <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
@@ -1314,16 +1304,14 @@
       <c r="J10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="49"/>
+      <c r="K10" s="76"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="13"/>
-      <c r="D11" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="60"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="63"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
@@ -1332,10 +1320,10 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="64"/>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
@@ -1347,36 +1335,36 @@
       <c r="K12" s="20"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1393,27 +1381,27 @@
       <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48" t="s">
+      <c r="D16" s="56"/>
+      <c r="E16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48" t="s">
+      <c r="F16" s="56"/>
+      <c r="G16" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48" t="s">
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="48" t="s">
+      <c r="K16" s="56" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1422,13 +1410,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>24</v>
@@ -1442,9 +1430,9 @@
       <c r="H17" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
@@ -1599,153 +1587,162 @@
       <c r="K27" s="26"/>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="75"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="80"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="43"/>
       <c r="K28" s="26"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="78"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="74"/>
+      <c r="B30" s="53"/>
       <c r="C30" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D30" s="33"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
       <c r="G30" s="33"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
       <c r="K30" s="34"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
-      <c r="B31" s="76" t="s">
+      <c r="B31" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="66"/>
+      <c r="C31" s="58"/>
       <c r="D31" s="35"/>
-      <c r="E31" s="67" t="s">
+      <c r="E31" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="67"/>
+      <c r="F31" s="59"/>
       <c r="G31" s="35"/>
-      <c r="H31" s="66" t="s">
+      <c r="H31" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="66"/>
-      <c r="J31" s="66"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="34"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="74" t="s">
+      <c r="A32" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="74"/>
+      <c r="B32" s="53"/>
       <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="33"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
       <c r="G32" s="33"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
       <c r="K32" s="34"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="68"/>
+      <c r="C33" s="55"/>
       <c r="D33" s="35"/>
-      <c r="E33" s="69" t="s">
+      <c r="E33" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="69"/>
+      <c r="F33" s="52"/>
       <c r="G33" s="35"/>
-      <c r="H33" s="68" t="s">
+      <c r="H33" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
       <c r="K33" s="34"/>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="70"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D34" s="35"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
       <c r="G34" s="35"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
       <c r="K34" s="34"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="36"/>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="72"/>
+      <c r="C35" s="51"/>
       <c r="D35" s="36"/>
-      <c r="E35" s="69" t="s">
+      <c r="E35" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="69"/>
+      <c r="F35" s="52"/>
       <c r="G35" s="36"/>
-      <c r="H35" s="69" t="s">
+      <c r="H35" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
       <c r="K35" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="K16:K17"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="E30:F30"/>
@@ -1759,27 +1756,18 @@
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:I17"/>
     <mergeCell ref="J16:J17"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="H35:J35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
